--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKAllergieUnvertraeglichkeit.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKAllergieUnvertraeglichkeit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-23</t>
+    <t>2025-12-11</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKAllergieUnvertraeglichkeit.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKAllergieUnvertraeglichkeit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11</t>
+    <t>2025-12-17</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKAllergieUnvertraeglichkeit.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKAllergieUnvertraeglichkeit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>0.0.1-rc</t>
   </si>
   <si>
     <t>Name</t>
